--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260322_0449PM</t>
+          <t>20260322_0536PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0449PM</t>
+          <t>0536PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260322_0536PM</t>
+          <t>20260322_0632PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0536PM</t>
+          <t>0632PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,29 +462,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260322_0632PM</t>
+          <t>20260326_1234PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260322</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0632PM</t>
+          <t>1234PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260326_1234PM</t>
+          <t>20260326_0835PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1234PM</t>
+          <t>0835PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260326_0835PM</t>
+          <t>20260326_0849PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0835PM</t>
+          <t>0849PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260326_0849PM</t>
+          <t>20260326_0916PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0849PM</t>
+          <t>0916PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260326_0916PM</t>
+          <t>20260326_1019PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0916PM</t>
+          <t>1019PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260326_1019PM</t>
+          <t>20260326_1045PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1019PM</t>
+          <t>1045PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,22 +469,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260326_1045PM</t>
+          <t>20260327_1008AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>20260327</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1045PM</t>
+          <t>1008AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_1008AM</t>
+          <t>20260327_1024AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1008AM</t>
+          <t>1024AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_1024AM</t>
+          <t>20260327_1040AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1024AM</t>
+          <t>1040AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_1040AM</t>
+          <t>20260327_1059AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1040AM</t>
+          <t>1059AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_1059AM</t>
+          <t>20260327_1112AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1059AM</t>
+          <t>1112AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_1112AM</t>
+          <t>20260327_0427PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1112AM</t>
+          <t>0427PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_0427PM</t>
+          <t>20260327_0452PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0427PM</t>
+          <t>0452PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_0452PM</t>
+          <t>20260327_0524PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0452PM</t>
+          <t>0524PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_0524PM</t>
+          <t>20260327_0535PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0524PM</t>
+          <t>0535PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_0535PM</t>
+          <t>20260327_0609PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0535PM</t>
+          <t>0609PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_0609PM</t>
+          <t>20260327_0619PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0609PM</t>
+          <t>0619PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,29 +462,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260327_0619PM</t>
+          <t>20260403_0536PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260327</t>
+          <t>20260403</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0619PM</t>
+          <t>0536PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260403_0536PM</t>
+          <t>20260403_0546PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0536PM</t>
+          <t>0546PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,22 +469,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260403_0546PM</t>
+          <t>20260405_1037AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260403</t>
+          <t>20260405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0546PM</t>
+          <t>1037AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260405_1037AM</t>
+          <t>20260405_1101AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1037AM</t>
+          <t>1101AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260405_1101AM</t>
+          <t>20260407_1219PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260405</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1101AM</t>
+          <t>1219PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,29 +462,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260407_1219PM</t>
+          <t>20260413_0750PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260413</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1219PM</t>
+          <t>0750PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260413_0750PM</t>
+          <t>20260413_0818PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0750PM</t>
+          <t>0818PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260413_0818PM</t>
+          <t>20260413_1125PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0818PM</t>
+          <t>1125PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260413_1125PM</t>
+          <t>20260413_1148PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1125PM</t>
+          <t>1148PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260413_1148PM</t>
+          <t>20260414_1208AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260413</t>
+          <t>20260414</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1148PM</t>
+          <t>1208AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260414_1208AM</t>
+          <t>20260414_1255AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1208AM</t>
+          <t>1255AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260414_1255AM</t>
+          <t>20260414_0113AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1255AM</t>
+          <t>0113AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -462,14 +462,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260414_0113AM</t>
+          <t>20260414_0117AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0113AM</t>
+          <t>0117AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260414_0117AM</t>
+          <t>20260414_0141AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0117AM</t>
+          <t>0141AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260414_0141AM</t>
+          <t>20260414_1203PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0141AM</t>
+          <t>1203PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260414_1222PM</t>
+          <t>20260414_0101PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1222PM</t>
+          <t>0101PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/presidencia/meta_data_reporte.xlsx
+++ b/presidencia/meta_data_reporte.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Mesas_Procesadas</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total_Mesas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Fecha_Hora</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Reporte</t>
         </is>
@@ -469,17 +457,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260414_0225PM</t>
+          <t>20260418_0602PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260414</t>
+          <t>20260418</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0225PM</t>
+          <t>0602PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
